--- a/knowledge_source/reference_data/excel/reference_data.xlsx
+++ b/knowledge_source/reference_data/excel/reference_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nielsenenterprise-my.sharepoint.com/personal/bavenraj_partipan_nielseniq_com/Documents/Hackfest Dataset/RAG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paba4001\Downloads\quintelligence\knowledge_source\reference_data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1170" documentId="11_F25DC773A252ABDACC10488DE1D858BA5BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7972D52-08D7-46DE-8CCF-6E29E8AA85C1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF455E0-1539-4ADB-BE20-2E93EC259D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="770" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Dictionary" sheetId="6" r:id="rId1"/>
@@ -25,13 +25,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data_Dictionary!$A$1:$H$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Proficiency_Level!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Proficiency_Level!$A$1:$E$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Relationship_Map!$A$1:$G$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Role_Master!$A$1:$D$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Role_Skill_Map!$A$1:$F$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Skill_Master!$A$1:$F$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Training_Catalogue!$A$1:$E$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Training_Skill_Map!$A$1:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Role_Skill_Map!$A$1:$E$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Skill_Master!$A$1:$D$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Training_Catalogue!$A$1:$C$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Training_Skill_Map!$A$1:$D$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3568,8 +3568,6 @@
     <col min="1" max="1" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="71" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -4250,7 +4248,6 @@
     <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -4261,7 +4258,7 @@
         <v>346</v>
       </c>
       <c r="C1" t="s">
-        <v>477</v>
+        <v>240</v>
       </c>
       <c r="D1" t="s">
         <v>232</v>
@@ -4931,8 +4928,6 @@
     <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.26953125" customWidth="1"/>
     <col min="4" max="4" width="69.54296875" customWidth="1"/>
-    <col min="5" max="5" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -4949,10 +4944,10 @@
         <v>239</v>
       </c>
       <c r="E1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F1" t="s">
         <v>301</v>
-      </c>
-      <c r="F1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -4969,10 +4964,10 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -4989,10 +4984,10 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -5009,10 +5004,10 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -5030,13 +5025,11 @@
     <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="164.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="85.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="94.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="97.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="87" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="89" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="97.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="87" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="89" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -5053,10 +5046,10 @@
         <v>92</v>
       </c>
       <c r="E1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F1" t="s">
         <v>301</v>
-      </c>
-      <c r="F1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -5073,10 +5066,10 @@
         <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -5093,10 +5086,10 @@
         <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -5113,10 +5106,10 @@
         <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -5133,10 +5126,10 @@
         <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -5153,10 +5146,10 @@
         <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -5173,10 +5166,10 @@
         <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -5193,10 +5186,10 @@
         <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -5213,10 +5206,10 @@
         <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -5233,10 +5226,10 @@
         <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -5253,10 +5246,10 @@
         <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -5273,10 +5266,10 @@
         <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -5293,10 +5286,10 @@
         <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -5313,10 +5306,10 @@
         <v>105</v>
       </c>
       <c r="E14" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -5333,10 +5326,10 @@
         <v>106</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -5353,10 +5346,10 @@
         <v>107</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -5373,10 +5366,10 @@
         <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -5393,10 +5386,10 @@
         <v>109</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -5413,10 +5406,10 @@
         <v>110</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -5433,10 +5426,10 @@
         <v>111</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -5453,10 +5446,10 @@
         <v>112</v>
       </c>
       <c r="E21" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -5473,10 +5466,10 @@
         <v>113</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -5493,10 +5486,10 @@
         <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -5513,10 +5506,10 @@
         <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -5533,10 +5526,10 @@
         <v>116</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -5553,10 +5546,10 @@
         <v>117</v>
       </c>
       <c r="E26" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -5573,10 +5566,10 @@
         <v>118</v>
       </c>
       <c r="E27" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -5593,10 +5586,10 @@
         <v>119</v>
       </c>
       <c r="E28" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -5613,10 +5606,10 @@
         <v>120</v>
       </c>
       <c r="E29" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -5633,10 +5626,10 @@
         <v>121</v>
       </c>
       <c r="E30" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -5653,10 +5646,10 @@
         <v>122</v>
       </c>
       <c r="E31" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -5673,10 +5666,10 @@
         <v>123</v>
       </c>
       <c r="E32" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -5693,10 +5686,10 @@
         <v>124</v>
       </c>
       <c r="E33" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -5713,10 +5706,10 @@
         <v>125</v>
       </c>
       <c r="E34" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -5733,10 +5726,10 @@
         <v>126</v>
       </c>
       <c r="E35" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -5753,10 +5746,10 @@
         <v>127</v>
       </c>
       <c r="E36" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -5773,10 +5766,10 @@
         <v>128</v>
       </c>
       <c r="E37" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -5793,10 +5786,10 @@
         <v>129</v>
       </c>
       <c r="E38" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -5813,10 +5806,10 @@
         <v>130</v>
       </c>
       <c r="E39" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="F39" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -5834,8 +5827,7 @@
     <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="110.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -5855,10 +5847,10 @@
         <v>142</v>
       </c>
       <c r="F1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G1" t="s">
         <v>301</v>
-      </c>
-      <c r="G1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -5878,10 +5870,10 @@
         <v>139</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -5901,10 +5893,10 @@
         <v>140</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -5924,10 +5916,10 @@
         <v>141</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -5944,9 +5936,8 @@
     <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -5960,13 +5951,13 @@
         <v>232</v>
       </c>
       <c r="D1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F1" t="s">
         <v>301</v>
-      </c>
-      <c r="E1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -5980,13 +5971,13 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E2" t="s">
-        <v>243</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -6000,13 +5991,13 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E3" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -6020,13 +6011,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E4" t="s">
-        <v>243</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -6040,13 +6031,13 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>243</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -6060,13 +6051,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>243</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -6080,13 +6071,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>243</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -6100,13 +6091,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>243</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -6120,13 +6111,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>243</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -6140,13 +6131,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>243</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -6160,13 +6151,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>243</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -6180,13 +6171,13 @@
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>243</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -6200,13 +6191,13 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>243</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -6220,13 +6211,13 @@
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -6240,13 +6231,13 @@
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>243</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -6260,13 +6251,13 @@
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>243</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -6280,13 +6271,13 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>243</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -6300,13 +6291,13 @@
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>243</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -6320,13 +6311,13 @@
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E19" t="s">
-        <v>244</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -6340,13 +6331,13 @@
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E20" t="s">
-        <v>244</v>
+        <v>34</v>
       </c>
       <c r="F20" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -6360,13 +6351,13 @@
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E21" t="s">
-        <v>244</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -6380,13 +6371,13 @@
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E22" t="s">
-        <v>244</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -6400,13 +6391,13 @@
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E23" t="s">
-        <v>244</v>
+        <v>15</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -6420,13 +6411,13 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E24" t="s">
-        <v>244</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -6440,13 +6431,13 @@
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E25" t="s">
-        <v>244</v>
+        <v>20</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -6460,13 +6451,13 @@
         <v>3</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E26" t="s">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -6480,13 +6471,13 @@
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E27" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -6500,13 +6491,13 @@
         <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E28" t="s">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c r="F28" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -6520,13 +6511,13 @@
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E29" t="s">
-        <v>244</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -6540,13 +6531,13 @@
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E30" t="s">
-        <v>244</v>
+        <v>46</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -6560,13 +6551,13 @@
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E31" t="s">
-        <v>244</v>
+        <v>47</v>
       </c>
       <c r="F31" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -6580,13 +6571,13 @@
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E32" t="s">
-        <v>244</v>
+        <v>30</v>
       </c>
       <c r="F32" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -6600,13 +6591,13 @@
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E33" t="s">
-        <v>244</v>
+        <v>32</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -6620,13 +6611,13 @@
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E34" t="s">
-        <v>244</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -6640,13 +6631,13 @@
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E35" t="s">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="F35" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -6660,13 +6651,13 @@
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E36" t="s">
-        <v>244</v>
+        <v>38</v>
       </c>
       <c r="F36" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -6680,13 +6671,13 @@
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E37" t="s">
-        <v>244</v>
+        <v>39</v>
       </c>
       <c r="F37" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -6700,13 +6691,13 @@
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E38" t="s">
-        <v>244</v>
+        <v>40</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -6720,13 +6711,13 @@
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E39" t="s">
-        <v>244</v>
+        <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -6740,13 +6731,13 @@
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E40" t="s">
-        <v>244</v>
+        <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -6760,13 +6751,13 @@
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E41" t="s">
-        <v>244</v>
+        <v>16</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -6780,13 +6771,13 @@
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E42" t="s">
-        <v>244</v>
+        <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -6800,13 +6791,13 @@
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E43" t="s">
-        <v>244</v>
+        <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -6820,13 +6811,13 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E44" t="s">
-        <v>244</v>
+        <v>22</v>
       </c>
       <c r="F44" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -6840,13 +6831,13 @@
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E45" t="s">
-        <v>244</v>
+        <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -6860,13 +6851,13 @@
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E46" t="s">
-        <v>244</v>
+        <v>24</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -6880,13 +6871,13 @@
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E47" t="s">
-        <v>244</v>
+        <v>25</v>
       </c>
       <c r="F47" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -6900,13 +6891,13 @@
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E48" t="s">
-        <v>244</v>
+        <v>31</v>
       </c>
       <c r="F48" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
@@ -6920,13 +6911,13 @@
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E49" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="F49" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -6940,13 +6931,13 @@
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E50" t="s">
-        <v>245</v>
+        <v>14</v>
       </c>
       <c r="F50" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -6960,13 +6951,13 @@
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E51" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="F51" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
@@ -6980,13 +6971,13 @@
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E52" t="s">
-        <v>245</v>
+        <v>34</v>
       </c>
       <c r="F52" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
@@ -7000,13 +6991,13 @@
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E53" t="s">
-        <v>245</v>
+        <v>36</v>
       </c>
       <c r="F53" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
@@ -7020,13 +7011,13 @@
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E54" t="s">
-        <v>245</v>
+        <v>41</v>
       </c>
       <c r="F54" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
@@ -7040,13 +7031,13 @@
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E55" t="s">
-        <v>245</v>
+        <v>11</v>
       </c>
       <c r="F55" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -7060,13 +7051,13 @@
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E56" t="s">
-        <v>245</v>
+        <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
@@ -7080,13 +7071,13 @@
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E57" t="s">
-        <v>245</v>
+        <v>13</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
@@ -7100,13 +7091,13 @@
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E58" t="s">
-        <v>245</v>
+        <v>15</v>
       </c>
       <c r="F58" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -7120,13 +7111,13 @@
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E59" t="s">
-        <v>245</v>
+        <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
@@ -7140,13 +7131,13 @@
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E60" t="s">
-        <v>245</v>
+        <v>17</v>
       </c>
       <c r="F60" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
@@ -7160,13 +7151,13 @@
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E61" t="s">
-        <v>245</v>
+        <v>18</v>
       </c>
       <c r="F61" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
@@ -7180,13 +7171,13 @@
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E62" t="s">
-        <v>245</v>
+        <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
@@ -7200,13 +7191,13 @@
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E63" t="s">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="F63" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
@@ -7220,13 +7211,13 @@
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E64" t="s">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="F64" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -7240,13 +7231,13 @@
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E65" t="s">
-        <v>245</v>
+        <v>22</v>
       </c>
       <c r="F65" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -7260,13 +7251,13 @@
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E66" t="s">
-        <v>245</v>
+        <v>23</v>
       </c>
       <c r="F66" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -7280,13 +7271,13 @@
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E67" t="s">
-        <v>245</v>
+        <v>24</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -7300,13 +7291,13 @@
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E68" t="s">
-        <v>245</v>
+        <v>25</v>
       </c>
       <c r="F68" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -7320,13 +7311,13 @@
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E69" t="s">
-        <v>245</v>
+        <v>26</v>
       </c>
       <c r="F69" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -7340,13 +7331,13 @@
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E70" t="s">
-        <v>245</v>
+        <v>27</v>
       </c>
       <c r="F70" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -7360,13 +7351,13 @@
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E71" t="s">
-        <v>245</v>
+        <v>28</v>
       </c>
       <c r="F71" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -7380,13 +7371,13 @@
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E72" t="s">
-        <v>245</v>
+        <v>29</v>
       </c>
       <c r="F72" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -7400,13 +7391,13 @@
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E73" t="s">
-        <v>245</v>
+        <v>43</v>
       </c>
       <c r="F73" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -7420,13 +7411,13 @@
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E74" t="s">
-        <v>245</v>
+        <v>44</v>
       </c>
       <c r="F74" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -7440,13 +7431,13 @@
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E75" t="s">
-        <v>245</v>
+        <v>45</v>
       </c>
       <c r="F75" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -7460,13 +7451,13 @@
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E76" t="s">
-        <v>245</v>
+        <v>46</v>
       </c>
       <c r="F76" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
@@ -7480,13 +7471,13 @@
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E77" t="s">
-        <v>245</v>
+        <v>48</v>
       </c>
       <c r="F77" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -7500,13 +7491,13 @@
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E78" t="s">
-        <v>245</v>
+        <v>30</v>
       </c>
       <c r="F78" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -7520,13 +7511,13 @@
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E79" t="s">
-        <v>245</v>
+        <v>31</v>
       </c>
       <c r="F79" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -7540,13 +7531,13 @@
         <v>3</v>
       </c>
       <c r="D80" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E80" t="s">
-        <v>245</v>
+        <v>32</v>
       </c>
       <c r="F80" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -7560,13 +7551,13 @@
         <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E81" t="s">
-        <v>245</v>
+        <v>33</v>
       </c>
       <c r="F81" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
@@ -7580,13 +7571,13 @@
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E82" t="s">
-        <v>245</v>
+        <v>35</v>
       </c>
       <c r="F82" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
@@ -7600,13 +7591,13 @@
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E83" t="s">
-        <v>245</v>
+        <v>37</v>
       </c>
       <c r="F83" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
@@ -7620,13 +7611,13 @@
         <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E84" t="s">
-        <v>245</v>
+        <v>38</v>
       </c>
       <c r="F84" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
@@ -7640,13 +7631,13 @@
         <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E85" t="s">
-        <v>245</v>
+        <v>39</v>
       </c>
       <c r="F85" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -7660,13 +7651,13 @@
         <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E86" t="s">
-        <v>245</v>
+        <v>40</v>
       </c>
       <c r="F86" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -7680,13 +7671,13 @@
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="E87" t="s">
-        <v>245</v>
+        <v>42</v>
       </c>
       <c r="F87" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
